--- a/SGC-CKN/Excel/b211cebb-0464-4843-8787-9239d72e9a52_P1_75_D800_12-11-2026.xlsx
+++ b/SGC-CKN/Excel/b211cebb-0464-4843-8787-9239d72e9a52_P1_75_D800_12-11-2026.xlsx
@@ -35,7 +35,7 @@
     <t>Số hiệu cọc</t>
   </si>
   <si>
-    <t>75</t>
+    <t>P1-75</t>
   </si>
   <si>
     <t>Tên Máy khoan</t>

--- a/SGC-CKN/Excel/b211cebb-0464-4843-8787-9239d72e9a52_P1_75_D800_12-11-2026.xlsx
+++ b/SGC-CKN/Excel/b211cebb-0464-4843-8787-9239d72e9a52_P1_75_D800_12-11-2026.xlsx
@@ -53,13 +53,13 @@
     <t>Bắt đầu thi công</t>
   </si>
   <si>
-    <t>19:00 11/11/2026</t>
+    <t>19:00 01/04/2026</t>
   </si>
   <si>
     <t>Kết thúc thi công</t>
   </si>
   <si>
-    <t>02:10 12/11/2026</t>
+    <t>02:10 02/04/2026</t>
   </si>
   <si>
     <t>Địa chất TT</t>
@@ -99,11 +99,11 @@
   </si>
   <si>
     <t xml:space="preserve">19:00
-11/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">19:10
-11/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t/>
@@ -116,7 +116,7 @@
   </si>
   <si>
     <t xml:space="preserve">19:30
-11/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>3</t>
@@ -126,7 +126,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:00
-11/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>4</t>
@@ -136,7 +136,7 @@
   </si>
   <si>
     <t xml:space="preserve">20:30
-11/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>5</t>
@@ -146,7 +146,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:00
-11/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>6</t>
@@ -156,7 +156,7 @@
   </si>
   <si>
     <t xml:space="preserve">21:30
-11/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>7</t>
@@ -166,7 +166,7 @@
   </si>
   <si>
     <t xml:space="preserve">23:53
-11/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>8</t>
@@ -176,11 +176,11 @@
   </si>
   <si>
     <t xml:space="preserve">01:00
-12/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:10
-12/11/2026</t>
+01/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>

--- a/SGC-CKN/Excel/b211cebb-0464-4843-8787-9239d72e9a52_P1_75_D800_12-11-2026.xlsx
+++ b/SGC-CKN/Excel/b211cebb-0464-4843-8787-9239d72e9a52_P1_75_D800_12-11-2026.xlsx
@@ -176,11 +176,11 @@
   </si>
   <si>
     <t xml:space="preserve">01:00
-01/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t xml:space="preserve">02:10
-01/04/2026</t>
+02/04/2026</t>
   </si>
   <si>
     <t>ẢNH BIÊN BẢN GỐC</t>
